--- a/03_PLANILHAS_CONTROLE/PLANILHA_VISUAL_AGENDA_DIA_A_DIA_OE.xlsx
+++ b/03_PLANILHAS_CONTROLE/PLANILHA_VISUAL_AGENDA_DIA_A_DIA_OE.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapa Visual" sheetId="1" r:id="R4a89cb04d7f34c43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vagas Abertas" sheetId="2" r:id="Rc0e025dd92044b06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapa Visual" sheetId="1" r:id="Rfe80de1a628c4536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vagas Abertas" sheetId="2" r:id="R08f485a40c9b471f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -517,7 +517,6 @@
 Douglas Nunes (18h às 00h)
 Nicolas Abreu (18h às 00h)
 Danilo Leite (18h às 00h)
-Luiz Guilherme (18h às 00h)
 Letícia Santana (18h às 00h)
 Everton Renato (18h às 00h)</x:v>
       </x:c>
@@ -569,7 +568,7 @@
       </x:c>
       <x:c r="H3" s="24" t="str">
         <x:v>Pedro Henrique (17h às 23h / 18h às 00h)
-Luiz Guilherme (17h às 23h / 18h às 00h)
+Luiz Guilherme (18h às 00h)
 Denis Ambrósio (17h às 23h / 18h às 00h)
 Gustavo (17h às 23h / 18h às 00h)</x:v>
       </x:c>
@@ -741,14 +740,12 @@
       <x:c r="H7" s="48" t="str">
         <x:v>Luiz Guilherme (Turno da manhã)
 Lucas Lima (Turno da manhã)
-Weslley Santos (Turno da tarde)
-Denilson Silveiro (Turno da tarde)</x:v>
+Weslley Santos (Turno da tarde)</x:v>
       </x:c>
       <x:c r="I7" s="48" t="str">
         <x:v>Luiz Guilherme (Turno da manhã)
 Lucas Lima (Turno da manhã)
-Weslley Santos (Turno da tarde)
-Denilson Silveiro (Turno da tarde)</x:v>
+Weslley Santos (Turno da tarde)</x:v>
       </x:c>
       <x:c r="J7" s="52" t="n">
         <x:v>0</x:v>

--- a/03_PLANILHAS_CONTROLE/PLANILHA_VISUAL_AGENDA_DIA_A_DIA_OE.xlsx
+++ b/03_PLANILHAS_CONTROLE/PLANILHA_VISUAL_AGENDA_DIA_A_DIA_OE.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapa Visual" sheetId="1" r:id="Rfe80de1a628c4536"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vagas Abertas" sheetId="2" r:id="R08f485a40c9b471f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapa Visual" sheetId="1" r:id="R4473a374c6c0450d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vagas Abertas" sheetId="2" r:id="Rdb4ef14461a44bb5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -474,7 +474,7 @@
         <x:v>Pizzaria Bevenutti · 18h às 00h</x:v>
       </x:c>
       <x:c r="C2" s="18" t="str">
-        <x:v>Roger Martineli (18h às 00h)
+        <x:v>Douglas Nunes (18h às 00h)
 Lucas Lima (18h às 00h)
 Alessandro Ignácio (18h às 00h)</x:v>
       </x:c>
